--- a/Desktop Files - Mix/02. Data - EclipseApps/01. Live Project/09. CSR_AUTH.xlsx
+++ b/Desktop Files - Mix/02. Data - EclipseApps/01. Live Project/09. CSR_AUTH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Visteon\00. Visteon Copy\ZPLM\GAP 33\02. CSR_Auth\DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05. Daily (21-Mar-26) - 6GB\VSCode\Desktop Files - Mix\02. Data - EclipseApps\01. Live Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978B8A9A-8079-41E4-8C80-042198FA46E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{872BA465-2988-42EF-AF6C-4B1C0558EC17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -421,8 +421,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -481,18 +494,12 @@
       <c r="G2" t="s">
         <v>16</v>
       </c>
-      <c r="H2">
-        <v>20250426221609.5</v>
-      </c>
-      <c r="I2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2">
-        <v>20250427202240.699</v>
-      </c>
-      <c r="K2">
-        <v>20250427202240.699</v>
-      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -513,18 +520,12 @@
       <c r="G3" t="s">
         <v>16</v>
       </c>
-      <c r="H3">
-        <v>20250427201506</v>
-      </c>
-      <c r="I3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3">
-        <v>20250427230501.699</v>
-      </c>
-      <c r="K3">
-        <v>20250427230501.699</v>
-      </c>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -548,18 +549,12 @@
       <c r="G4" t="s">
         <v>16</v>
       </c>
-      <c r="H4">
-        <v>20250430121952.199</v>
-      </c>
-      <c r="I4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4">
-        <v>20250504015112.301</v>
-      </c>
-      <c r="K4">
-        <v>20250504015112.301</v>
-      </c>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -583,18 +578,12 @@
       <c r="G5" t="s">
         <v>16</v>
       </c>
-      <c r="H5">
-        <v>20250427154634.602</v>
-      </c>
-      <c r="I5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5">
-        <v>20250504015144.301</v>
-      </c>
-      <c r="K5">
-        <v>20250504015144.301</v>
-      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -615,18 +604,12 @@
       <c r="G6" t="s">
         <v>16</v>
       </c>
-      <c r="H6">
-        <v>20250502185914</v>
-      </c>
-      <c r="I6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6">
-        <v>20250504015317.898</v>
-      </c>
-      <c r="K6">
-        <v>20250504015317.898</v>
-      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -650,18 +633,12 @@
       <c r="G7" t="s">
         <v>16</v>
       </c>
-      <c r="H7">
-        <v>20250504022411.699</v>
-      </c>
-      <c r="I7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7">
-        <v>20250504022411.699</v>
-      </c>
-      <c r="K7">
-        <v>20250504022411.699</v>
-      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -685,18 +662,54 @@
       <c r="G8" t="s">
         <v>16</v>
       </c>
-      <c r="H8">
-        <v>20250426221316.699</v>
-      </c>
-      <c r="I8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8">
-        <v>20250504151709.102</v>
-      </c>
-      <c r="K8">
-        <v>20250504151709.102</v>
-      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
